--- a/data/projects/drum-pilot/raw/드럼Pilot_샘플.xlsx
+++ b/data/projects/drum-pilot/raw/드럼Pilot_샘플.xlsx
@@ -507,7 +507,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -535,7 +535,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -563,7 +563,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -591,7 +591,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -619,7 +619,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -647,7 +647,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -675,7 +675,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -703,7 +703,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -731,7 +731,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -759,7 +759,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -787,7 +787,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -815,7 +815,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -843,7 +843,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -871,7 +871,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -899,7 +899,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -927,7 +927,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -955,7 +955,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -983,7 +983,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1011,7 +1011,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -1039,7 +1039,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1067,7 +1067,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -1095,7 +1095,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1123,7 +1123,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -1151,7 +1151,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1179,7 +1179,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -1207,7 +1207,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1235,7 +1235,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -1263,7 +1263,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1291,7 +1291,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -1319,7 +1319,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1347,7 +1347,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -1375,7 +1375,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1403,7 +1403,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -1431,7 +1431,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1459,7 +1459,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -1487,7 +1487,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1638,7 +1638,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1713,7 +1713,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1788,7 +1788,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1863,7 +1863,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1938,7 +1938,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -2088,7 +2088,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -2163,7 +2163,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -2238,7 +2238,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
